--- a/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_LA SALUD CARTAGENA C.B..xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_LA SALUD CARTAGENA C.B..xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,7 +853,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. YAÑEZ GAMBIN</t>
+          <t>C. TOLEDO ZAMORA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -862,76 +862,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5918</v>
+        <v>-1.0073</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5918</v>
+        <v>0.1950000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-1.2024</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5918</v>
+        <v>-1.3778</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0.6034999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5918</v>
+        <v>-0.7743</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5918</v>
+        <v>1.122</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-0.3771</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5918</v>
+        <v>1.4992</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-2.4997</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.2263</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-2.2734</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0548</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.0274</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.1101</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.1804</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.2905</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.2877</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.3082</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.0205</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. TOLEDO ZAMORA</t>
+          <t>A. MORENO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -940,76 +940,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0073</v>
+        <v>-1.1577</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1950000000000001</v>
+        <v>0.9282</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2024</v>
+        <v>-2.0859</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3778</v>
+        <v>-0.7997</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6034999999999999</v>
+        <v>-2.157</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7743</v>
+        <v>1.3573</v>
       </c>
       <c r="J7" t="n">
-        <v>1.122</v>
+        <v>1.116</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3771</v>
+        <v>-1.3312</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4992</v>
+        <v>2.4472</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.4997</v>
+        <v>-1.9157</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2263</v>
+        <v>-0.8258</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.2734</v>
+        <v>-1.0899</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.0274</v>
+        <v>0.8219</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0548</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0274</v>
+        <v>0.8219</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1101</v>
+        <v>-0.5909</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1804</v>
+        <v>-0.1878</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2905</v>
+        <v>-0.4031</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2877</v>
+        <v>-0.589</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3082</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0205</v>
+        <v>-0.589</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MORENO</t>
+          <t>D. YANEZ GAMBIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1018,76 +1018,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1577</v>
+        <v>-1.8007</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9282</v>
+        <v>-1.5756</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0859</v>
+        <v>-0.2252</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7997</v>
+        <v>-1.6101</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.157</v>
+        <v>-0.4589</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3573</v>
+        <v>-1.1512</v>
       </c>
       <c r="J8" t="n">
-        <v>1.116</v>
+        <v>-1.478</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3312</v>
+        <v>-0.6901</v>
       </c>
       <c r="L8" t="n">
-        <v>2.4472</v>
+        <v>-0.7879</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9157</v>
+        <v>-0.1321</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8258</v>
+        <v>0.2312</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0899</v>
+        <v>-0.3633</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8219</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8219</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5909</v>
+        <v>-0.1907</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1878</v>
+        <v>-0.09760000000000002</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4031</v>
+        <v>-0.0931</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.589</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. YANEZ GAMBIN</t>
+          <t>G. GIL GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1096,76 +1096,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3925</v>
+        <v>-5.3447</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1674</v>
+        <v>-1.7427</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2252</v>
+        <v>-3.6018</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2018</v>
+        <v>-6.8462</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4589</v>
+        <v>-2.5411</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.743</v>
+        <v>-4.305</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.0698</v>
+        <v>0.1822</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6901</v>
+        <v>0.5676</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3797</v>
+        <v>-0.3853999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1321</v>
+        <v>-7.0283</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2312</v>
+        <v>-3.1087</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3633</v>
+        <v>-3.9197</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.4384</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.0822</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>4.5206</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1907</v>
+        <v>2.6712</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.09760000000000002</v>
+        <v>-0.2604999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0931</v>
+        <v>2.9318</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.6083</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.4178</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-4.026</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. GIL GARCIA</t>
+          <t>I. ALVAREZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1177,73 +1177,73 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.3447</v>
+        <v>-6.3322</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7427</v>
+        <v>-2.7753</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.6018</v>
+        <v>-3.557</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.8462</v>
+        <v>-2.1789</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5411</v>
+        <v>-0.5477000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.305</v>
+        <v>-1.6312</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1822</v>
+        <v>3.8758</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5676</v>
+        <v>0.6733</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3853999999999999</v>
+        <v>3.2025</v>
       </c>
       <c r="M10" t="n">
-        <v>-7.0283</v>
+        <v>-6.054600000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.1087</v>
+        <v>-1.2209</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.9197</v>
+        <v>-4.8336</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4384</v>
+        <v>-2.4658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0822</v>
+        <v>-7.191800000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>4.5206</v>
+        <v>4.726</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6712</v>
+        <v>-0.4889000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2604999999999999</v>
+        <v>-0.8768000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>2.9318</v>
+        <v>0.3879</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.6083</v>
+        <v>-1.1986</v>
       </c>
       <c r="W10" t="n">
         <v>1.4178</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.026</v>
+        <v>-2.6164</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. ALVAREZ FERNANDEZ</t>
+          <t>J. MARTINEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,73 +1255,73 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.3322</v>
+        <v>-7.342499999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7753</v>
+        <v>-1.6909</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.557</v>
+        <v>-5.6515</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1789</v>
+        <v>1.3979</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5477000000000001</v>
+        <v>1.4709</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6312</v>
+        <v>-0.07300000000000012</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8758</v>
+        <v>4.6782</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6733</v>
+        <v>1.9554</v>
       </c>
       <c r="L11" t="n">
-        <v>3.2025</v>
+        <v>2.7229</v>
       </c>
       <c r="M11" t="n">
-        <v>-6.054600000000001</v>
+        <v>-3.2803</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2209</v>
+        <v>-0.4844</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.8336</v>
+        <v>-2.7957</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.4658</v>
+        <v>-3.0823</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.191800000000001</v>
+        <v>-5.137</v>
       </c>
       <c r="R11" t="n">
-        <v>4.726</v>
+        <v>2.0548</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4889000000000001</v>
+        <v>-1.0555</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8768000000000001</v>
+        <v>-0.8827</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3879</v>
+        <v>-0.1728</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1986</v>
+        <v>-4.602600000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4178</v>
+        <v>-0.3493</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.6164</v>
+        <v>-4.2533</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANCHEZ</t>
+          <t>K. SOW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1333,73 +1333,73 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.342499999999999</v>
+        <v>-11.8251</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6909</v>
+        <v>-3.6381</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.6515</v>
+        <v>-8.187099999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3979</v>
+        <v>-10.0767</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4709</v>
+        <v>-5.6412</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.07300000000000012</v>
+        <v>-4.435700000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>4.6782</v>
+        <v>-2.6947</v>
       </c>
       <c r="K12" t="n">
-        <v>1.9554</v>
+        <v>-3.5639</v>
       </c>
       <c r="L12" t="n">
-        <v>2.7229</v>
+        <v>0.8691</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.2803</v>
+        <v>-7.382099999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4844</v>
+        <v>-2.0773</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.7957</v>
+        <v>-5.3046</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.0823</v>
+        <v>1.4384</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.137</v>
+        <v>-1.0274</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0548</v>
+        <v>2.4658</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0555</v>
+        <v>0.5913000000000002</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8827</v>
+        <v>0.08410000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1728</v>
+        <v>0.5072</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.602600000000001</v>
+        <v>-3.7781</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3493</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.2533</v>
+        <v>-3.7781</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. SOW</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1411,144 +1411,66 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.8251</v>
+        <v>-4.399199999999995</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6381</v>
+        <v>42.35489999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.187099999999999</v>
+        <v>-46.7541</v>
       </c>
       <c r="G13" t="n">
-        <v>-10.0767</v>
+        <v>-4.599299999999998</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.6412</v>
+        <v>-2.555800000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.435700000000001</v>
+        <v>-2.0435</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.6947</v>
+        <v>61.6173</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.5639</v>
+        <v>17.5385</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8691</v>
+        <v>44.07860000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.382099999999999</v>
+        <v>-66.21639999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.0773</v>
+        <v>-20.0943</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.3046</v>
+        <v>-46.12199999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>1.4384</v>
+        <v>2.0549</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0274</v>
+        <v>-34.9316</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4658</v>
+        <v>36.9866</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5913000000000002</v>
+        <v>3.3778</v>
       </c>
       <c r="T13" t="n">
-        <v>0.08410000000000001</v>
+        <v>-5.9672</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5072</v>
+        <v>9.344999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.7781</v>
+        <v>-5.233000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>21.6369</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.7781</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>LA SALUD CARTAGENA C.B.</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-4.399199999999995</v>
-      </c>
-      <c r="E14" t="n">
-        <v>42.35489999999999</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-46.7541</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-4.599199999999998</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-2.555800000000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-2.043500000000002</v>
-      </c>
-      <c r="J14" t="n">
-        <v>61.6173</v>
-      </c>
-      <c r="K14" t="n">
-        <v>17.5385</v>
-      </c>
-      <c r="L14" t="n">
-        <v>44.07860000000001</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-66.21639999999999</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-20.0943</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-46.12199999999999</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.0549</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-34.9316</v>
-      </c>
-      <c r="R14" t="n">
-        <v>36.9866</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.3778</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-5.9672</v>
-      </c>
-      <c r="U14" t="n">
-        <v>9.344999999999999</v>
-      </c>
-      <c r="V14" t="n">
-        <v>-5.233000000000001</v>
-      </c>
-      <c r="W14" t="n">
-        <v>21.6369</v>
-      </c>
-      <c r="X14" t="n">
         <v>-26.8694</v>
       </c>
     </row>
